--- a/01_Input/00_CO Validation/Cabo Verde - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Cabo Verde - Energy Projects.xlsx
@@ -1072,8 +1072,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd739a91710fed73edeed3c312976475">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="829e6ebd84bdd7e43dc34d34aecb984e" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -1097,6 +1097,7 @@
                 <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1172,6 +1173,11 @@
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="fb9e4d32-074f-4c04-81ef-e811753dfd59" elementFormDefault="qualified">
@@ -1330,7 +1336,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{192F818E-73F8-4DE1-AC85-AC0A374A0761}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{473F3DBB-9B4D-46F3-BA9F-66A79B3C3FDD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/01_Input/00_CO Validation/Cabo Verde - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Cabo Verde - Energy Projects.xlsx
@@ -1,23 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28318"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A671246-EDD2-4A8C-BCC0-84A494FC8939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{6A671246-EDD2-4A8C-BCC0-84A494FC8939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7FCBE2B-8E7B-40EC-9C26-5EB7A68AEFA2}"/>
   <bookViews>
     <workbookView xWindow="30" yWindow="20" windowWidth="19170" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Projects" sheetId="1" r:id="rId1"/>
+    <sheet name="Projects (3)" sheetId="1" r:id="rId1"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -417,7 +420,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1063,17 +1066,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -1098,6 +1103,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1177,6 +1183,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -1321,24 +1332,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{473F3DBB-9B4D-46F3-BA9F-66A79B3C3FDD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CC3E6F4-AE33-4BCB-83CB-AFF165102463}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84AEDBCE-AE29-4AA3-A5BD-B932231712F2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D06A8A7-AAD0-46D5-9E3E-4D298B186157}"/>
 </file>
--- a/01_Input/00_CO Validation/Cabo Verde - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Cabo Verde - Energy Projects.xlsx
@@ -869,13 +869,7 @@
       <c r="B14" s="13" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
+  <dataValidations count="1">
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
